--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/116.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/116.xlsx
@@ -426,13 +426,13 @@
         <v>-16.35066352153666</v>
       </c>
       <c r="E2">
-        <v>-17.60320850812202</v>
+        <v>-19.1618730337701</v>
       </c>
       <c r="F2">
-        <v>0.6782877913497974</v>
+        <v>-1.546545520926129</v>
       </c>
       <c r="G2">
-        <v>-17.16837219294744</v>
+        <v>-18.37299065795858</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.48960543009377</v>
       </c>
       <c r="E3">
-        <v>-18.79589987836621</v>
+        <v>-22.61605715260082</v>
       </c>
       <c r="F3">
-        <v>0.8875184866837021</v>
+        <v>-1.638136447918864</v>
       </c>
       <c r="G3">
-        <v>-16.67304226755522</v>
+        <v>-18.08271083025918</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.5811116813372</v>
       </c>
       <c r="E4">
-        <v>-18.99842682141125</v>
+        <v>-22.81604815020156</v>
       </c>
       <c r="F4">
-        <v>0.7861561378075435</v>
+        <v>-2.068992700034763</v>
       </c>
       <c r="G4">
-        <v>-16.25123139242393</v>
+        <v>-18.37190949545474</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.61009428533848</v>
       </c>
       <c r="E5">
-        <v>-19.18661661574801</v>
+        <v>-23.02694371321278</v>
       </c>
       <c r="F5">
-        <v>0.8507588548170713</v>
+        <v>-1.812702452547818</v>
       </c>
       <c r="G5">
-        <v>-16.37163253632619</v>
+        <v>-17.79273943738637</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.58376324808466</v>
       </c>
       <c r="E6">
-        <v>-19.55802846843511</v>
+        <v>-23.73384303428413</v>
       </c>
       <c r="F6">
-        <v>1.091875068219535</v>
+        <v>-1.817734784519825</v>
       </c>
       <c r="G6">
-        <v>-16.11231267465093</v>
+        <v>-16.84141158943501</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.50793098858385</v>
       </c>
       <c r="E7">
-        <v>-20.79656158105895</v>
+        <v>-25.0134312922615</v>
       </c>
       <c r="F7">
-        <v>1.342032083456152</v>
+        <v>-1.213731521135968</v>
       </c>
       <c r="G7">
-        <v>-15.38302837084875</v>
+        <v>-17.49358554597946</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.38482735898232</v>
       </c>
       <c r="E8">
-        <v>-21.07504461863464</v>
+        <v>-25.06779109424958</v>
       </c>
       <c r="F8">
-        <v>1.221395281851654</v>
+        <v>-1.633437948010186</v>
       </c>
       <c r="G8">
-        <v>-14.73757271544726</v>
+        <v>-17.28422228254675</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.20602928857987</v>
       </c>
       <c r="E9">
-        <v>-21.6576146858254</v>
+        <v>-26.06098507055986</v>
       </c>
       <c r="F9">
-        <v>1.454716557993774</v>
+        <v>-1.598378126054099</v>
       </c>
       <c r="G9">
-        <v>-14.06907140042301</v>
+        <v>-15.56602209721898</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.97033769774324</v>
       </c>
       <c r="E10">
-        <v>-22.65782779684757</v>
+        <v>-26.59015537225217</v>
       </c>
       <c r="F10">
-        <v>1.501678362793284</v>
+        <v>-1.248753238191526</v>
       </c>
       <c r="G10">
-        <v>-14.20539959377482</v>
+        <v>-15.2048580401709</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.66506256729818</v>
       </c>
       <c r="E11">
-        <v>-23.45600756849153</v>
+        <v>-26.32868128304928</v>
       </c>
       <c r="F11">
-        <v>1.535919757755404</v>
+        <v>-1.324251471650076</v>
       </c>
       <c r="G11">
-        <v>-14.08063770642006</v>
+        <v>-16.18450283018028</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.29640532720239</v>
       </c>
       <c r="E12">
-        <v>-23.98182679941817</v>
+        <v>-26.95914449134516</v>
       </c>
       <c r="F12">
-        <v>1.608030796903906</v>
+        <v>-0.8077470002891253</v>
       </c>
       <c r="G12">
-        <v>-13.09796270830054</v>
+        <v>-15.49225695534111</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.85980033078623</v>
       </c>
       <c r="E13">
-        <v>-24.28630327779789</v>
+        <v>-26.64317021745996</v>
       </c>
       <c r="F13">
-        <v>2.020037548769102</v>
+        <v>-0.4113939072346318</v>
       </c>
       <c r="G13">
-        <v>-12.61614485329011</v>
+        <v>-14.55667733026429</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.37666129010475</v>
       </c>
       <c r="E14">
-        <v>-25.51367823046683</v>
+        <v>-27.00500434762084</v>
       </c>
       <c r="F14">
-        <v>2.050029418954861</v>
+        <v>-0.5980126575743184</v>
       </c>
       <c r="G14">
-        <v>-12.15845382040629</v>
+        <v>-14.17868388783782</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.85734295493638</v>
       </c>
       <c r="E15">
-        <v>-26.19279083502711</v>
+        <v>-29.21289807785259</v>
       </c>
       <c r="F15">
-        <v>2.527579913199165</v>
+        <v>-0.5700345485447651</v>
       </c>
       <c r="G15">
-        <v>-11.89642531033371</v>
+        <v>-14.2597546695178</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.31979935929133</v>
       </c>
       <c r="E16">
-        <v>-27.80663934493266</v>
+        <v>-30.26209569221572</v>
       </c>
       <c r="F16">
-        <v>2.759067183911487</v>
+        <v>-0.03248954515270716</v>
       </c>
       <c r="G16">
-        <v>-11.26178127997059</v>
+        <v>-13.34562603038586</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.78220243321929</v>
       </c>
       <c r="E17">
-        <v>-28.38831730274391</v>
+        <v>-31.24441000972257</v>
       </c>
       <c r="F17">
-        <v>2.819711961470439</v>
+        <v>-0.1151713807283342</v>
       </c>
       <c r="G17">
-        <v>-11.53911012617486</v>
+        <v>-13.48070735954508</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.25662175633855</v>
       </c>
       <c r="E18">
-        <v>-28.51162764997277</v>
+        <v>-33.23666233618307</v>
       </c>
       <c r="F18">
-        <v>3.223307470727608</v>
+        <v>-0.3886974687653282</v>
       </c>
       <c r="G18">
-        <v>-11.20851392917457</v>
+        <v>-12.7268762372567</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.76214975698353</v>
       </c>
       <c r="E19">
-        <v>-29.2848736437305</v>
+        <v>-33.24030775775924</v>
       </c>
       <c r="F19">
-        <v>3.618828054542288</v>
+        <v>-0.0969348723557031</v>
       </c>
       <c r="G19">
-        <v>-11.00973424588185</v>
+        <v>-12.42528275762033</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.30232947276376</v>
       </c>
       <c r="E20">
-        <v>-30.78081880437234</v>
+        <v>-34.72182520021264</v>
       </c>
       <c r="F20">
-        <v>3.758813861941376</v>
+        <v>0.5801933518776827</v>
       </c>
       <c r="G20">
-        <v>-10.78332011461548</v>
+        <v>-13.11660989042286</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.892816423635</v>
       </c>
       <c r="E21">
-        <v>-30.68217279082625</v>
+        <v>-33.77331141269904</v>
       </c>
       <c r="F21">
-        <v>3.716013774973532</v>
+        <v>0.7011788961587589</v>
       </c>
       <c r="G21">
-        <v>-10.27468811702128</v>
+        <v>-12.72457938216508</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.52807768448523</v>
       </c>
       <c r="E22">
-        <v>-31.06107473952204</v>
+        <v>-34.81637520901879</v>
       </c>
       <c r="F22">
-        <v>3.84124304545915</v>
+        <v>0.9209000362817167</v>
       </c>
       <c r="G22">
-        <v>-9.969321232591557</v>
+        <v>-12.77016211206889</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.2100781276024</v>
       </c>
       <c r="E23">
-        <v>-31.39108954706802</v>
+        <v>-34.86327661431623</v>
       </c>
       <c r="F23">
-        <v>3.759963635896462</v>
+        <v>0.9234249001254495</v>
       </c>
       <c r="G23">
-        <v>-10.24574118042386</v>
+        <v>-11.46438030515851</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.930793193576704</v>
       </c>
       <c r="E24">
-        <v>-31.8676955867163</v>
+        <v>-35.6903888063952</v>
       </c>
       <c r="F24">
-        <v>4.139569625168558</v>
+        <v>1.387227808952893</v>
       </c>
       <c r="G24">
-        <v>-10.38151484733212</v>
+        <v>-12.30974766529073</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.681041658401359</v>
       </c>
       <c r="E25">
-        <v>-32.41077736056017</v>
+        <v>-33.93564814892601</v>
       </c>
       <c r="F25">
-        <v>4.050535039980861</v>
+        <v>1.00104789597218</v>
       </c>
       <c r="G25">
-        <v>-9.945184566800283</v>
+        <v>-12.07294518656716</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.455200752884878</v>
       </c>
       <c r="E26">
-        <v>-31.86631213790696</v>
+        <v>-36.73547456635937</v>
       </c>
       <c r="F26">
-        <v>4.185350178051675</v>
+        <v>1.152036079215252</v>
       </c>
       <c r="G26">
-        <v>-10.34300314988892</v>
+        <v>-12.5008689774637</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.239706207868988</v>
       </c>
       <c r="E27">
-        <v>-31.85054399141225</v>
+        <v>-35.04325402104008</v>
       </c>
       <c r="F27">
-        <v>4.106484631100746</v>
+        <v>1.490357893866626</v>
       </c>
       <c r="G27">
-        <v>-9.883904472956093</v>
+        <v>-11.65650567112867</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.032762947228157</v>
       </c>
       <c r="E28">
-        <v>-32.57670291243822</v>
+        <v>-35.4209944161529</v>
       </c>
       <c r="F28">
-        <v>3.872812127179839</v>
+        <v>0.8635074291461556</v>
       </c>
       <c r="G28">
-        <v>-9.762230215088763</v>
+        <v>-13.58303553509793</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.822616311921847</v>
       </c>
       <c r="E29">
-        <v>-31.1213328789051</v>
+        <v>-35.06507673728304</v>
       </c>
       <c r="F29">
-        <v>3.925994971174373</v>
+        <v>0.6797134116500154</v>
       </c>
       <c r="G29">
-        <v>-10.2690312910528</v>
+        <v>-12.74684903288903</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.613730992507461</v>
       </c>
       <c r="E30">
-        <v>-30.59436794405453</v>
+        <v>-34.0992981426152</v>
       </c>
       <c r="F30">
-        <v>3.920093681796829</v>
+        <v>0.742057170752109</v>
       </c>
       <c r="G30">
-        <v>-9.531589870453836</v>
+        <v>-12.14853796885365</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.408066485901134</v>
       </c>
       <c r="E31">
-        <v>-30.87759682239026</v>
+        <v>-34.84970251347824</v>
       </c>
       <c r="F31">
-        <v>3.612487730441261</v>
+        <v>0.8867978070432666</v>
       </c>
       <c r="G31">
-        <v>-10.19996157722649</v>
+        <v>-11.50593041376576</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.211653436570835</v>
       </c>
       <c r="E32">
-        <v>-29.72970790974096</v>
+        <v>-34.62677705926565</v>
       </c>
       <c r="F32">
-        <v>3.854006530401485</v>
+        <v>0.9186965789902699</v>
       </c>
       <c r="G32">
-        <v>-10.10501615018239</v>
+        <v>-11.93260405924815</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.039062116745288</v>
       </c>
       <c r="E33">
-        <v>-29.75805162855497</v>
+        <v>-33.71382764237129</v>
       </c>
       <c r="F33">
-        <v>3.672575845105531</v>
+        <v>0.5653225002626261</v>
       </c>
       <c r="G33">
-        <v>-9.484543715734517</v>
+        <v>-13.2477898471479</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.898844038999865</v>
       </c>
       <c r="E34">
-        <v>-29.74447752771698</v>
+        <v>-32.80959100946769</v>
       </c>
       <c r="F34">
-        <v>3.80982472660577</v>
+        <v>0.3528421196075389</v>
       </c>
       <c r="G34">
-        <v>-9.895762807671927</v>
+        <v>-11.32377339889318</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.806018139060519</v>
       </c>
       <c r="E35">
-        <v>-29.7100701822067</v>
+        <v>-32.98662037961254</v>
       </c>
       <c r="F35">
-        <v>3.451774513889323</v>
+        <v>0.3565217276107743</v>
       </c>
       <c r="G35">
-        <v>-9.956081503599199</v>
+        <v>-12.16830076630618</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.762996664862014</v>
       </c>
       <c r="E36">
-        <v>-28.98520187627291</v>
+        <v>-33.03468560272995</v>
       </c>
       <c r="F36">
-        <v>3.390886196313948</v>
+        <v>0.2556911906072128</v>
       </c>
       <c r="G36">
-        <v>-9.507994606219869</v>
+        <v>-10.95908859111182</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.77623761602279</v>
       </c>
       <c r="E37">
-        <v>-27.66542793995147</v>
+        <v>-32.44428353974293</v>
       </c>
       <c r="F37">
-        <v>3.442478574895107</v>
+        <v>0.8568307878795917</v>
       </c>
       <c r="G37">
-        <v>-10.00649091041695</v>
+        <v>-13.18753677565182</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.842306056111614</v>
       </c>
       <c r="E38">
-        <v>-27.93059273547061</v>
+        <v>-31.46018047500305</v>
       </c>
       <c r="F38">
-        <v>3.385410687781443</v>
+        <v>0.5479541209281288</v>
       </c>
       <c r="G38">
-        <v>-10.14820030712625</v>
+        <v>-12.48581473294897</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.953018479019884</v>
       </c>
       <c r="E39">
-        <v>-27.10411452975272</v>
+        <v>-30.15288474880974</v>
       </c>
       <c r="F39">
-        <v>3.613690519910126</v>
+        <v>0.4403268293845974</v>
       </c>
       <c r="G39">
-        <v>-9.880688875827838</v>
+        <v>-11.70009341832434</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.102211738885584</v>
       </c>
       <c r="E40">
-        <v>-27.17964041925264</v>
+        <v>-30.36535622077563</v>
       </c>
       <c r="F40">
-        <v>3.698969287293529</v>
+        <v>0.7926836729416036</v>
       </c>
       <c r="G40">
-        <v>-10.08110916990028</v>
+        <v>-12.89884834040875</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.274369184551549</v>
       </c>
       <c r="E41">
-        <v>-27.05018946126938</v>
+        <v>-28.86416935146991</v>
       </c>
       <c r="F41">
-        <v>3.371232351315127</v>
+        <v>0.6070548216482623</v>
       </c>
       <c r="G41">
-        <v>-10.27465858602725</v>
+        <v>-12.13229264091284</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.460836921972785</v>
       </c>
       <c r="E42">
-        <v>-25.92438365211848</v>
+        <v>-28.87102998959153</v>
       </c>
       <c r="F42">
-        <v>3.562707819737427</v>
+        <v>0.3401523593640532</v>
       </c>
       <c r="G42">
-        <v>-9.880403409552166</v>
+        <v>-12.22603385964461</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.645942400631011</v>
       </c>
       <c r="E43">
-        <v>-25.4298878759029</v>
+        <v>-27.67001528412124</v>
       </c>
       <c r="F43">
-        <v>3.538039038482058</v>
+        <v>0.2505743651601203</v>
       </c>
       <c r="G43">
-        <v>-10.33276245740189</v>
+        <v>-11.89469938779344</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.82189663106424</v>
       </c>
       <c r="E44">
-        <v>-24.58791776060477</v>
+        <v>-28.4691369783588</v>
       </c>
       <c r="F44">
-        <v>3.622587185816192</v>
+        <v>0.4015608916683862</v>
       </c>
       <c r="G44">
-        <v>-10.31830539521098</v>
+        <v>-12.20407592496881</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.978786496509715</v>
       </c>
       <c r="E45">
-        <v>-24.56125863412161</v>
+        <v>-29.13559249806764</v>
       </c>
       <c r="F45">
-        <v>3.630691932485183</v>
+        <v>0.8363187542514703</v>
       </c>
       <c r="G45">
-        <v>-10.480118836415</v>
+        <v>-12.35002794115447</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.110520350267484</v>
       </c>
       <c r="E46">
-        <v>-24.3830133687057</v>
+        <v>-28.04181205709899</v>
       </c>
       <c r="F46">
-        <v>4.024461347610345</v>
+        <v>0.66453523572852</v>
       </c>
       <c r="G46">
-        <v>-10.40756446529255</v>
+        <v>-12.83914979535621</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.216984022850202</v>
       </c>
       <c r="E47">
-        <v>-23.67278561923871</v>
+        <v>-26.72509936920674</v>
       </c>
       <c r="F47">
-        <v>3.289908209912688</v>
+        <v>0.691291502838944</v>
       </c>
       <c r="G47">
-        <v>-10.55268961364523</v>
+        <v>-13.64683888832133</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.293744548111571</v>
       </c>
       <c r="E48">
-        <v>-22.63520354070525</v>
+        <v>-26.80909350510101</v>
       </c>
       <c r="F48">
-        <v>3.784844479206948</v>
+        <v>0.4691656121456594</v>
       </c>
       <c r="G48">
-        <v>-10.73648395807597</v>
+        <v>-13.05480808235072</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.347445161989242</v>
       </c>
       <c r="E49">
-        <v>-22.46073955108574</v>
+        <v>-27.70761067533292</v>
       </c>
       <c r="F49">
-        <v>3.480674595838192</v>
+        <v>0.6128509083656505</v>
       </c>
       <c r="G49">
-        <v>-10.8790727221632</v>
+        <v>-13.20171493401018</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.37843429458127</v>
       </c>
       <c r="E50">
-        <v>-21.90127375828211</v>
+        <v>-25.46215325320755</v>
       </c>
       <c r="F50">
-        <v>3.73305991938834</v>
+        <v>0.8957226374410284</v>
       </c>
       <c r="G50">
-        <v>-10.55201368200399</v>
+        <v>-12.60340715119635</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.39548314922895</v>
       </c>
       <c r="E51">
-        <v>-21.9477902432889</v>
+        <v>-25.88302962748044</v>
       </c>
       <c r="F51">
-        <v>3.647890496502106</v>
+        <v>0.1347304973482207</v>
       </c>
       <c r="G51">
-        <v>-10.77835562639604</v>
+        <v>-12.59111569523467</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.40129044211467</v>
       </c>
       <c r="E52">
-        <v>-21.62274543596634</v>
+        <v>-23.76397097185716</v>
       </c>
       <c r="F52">
-        <v>3.608451924454822</v>
+        <v>1.069558850388116</v>
       </c>
       <c r="G52">
-        <v>-10.64247039795476</v>
+        <v>-13.21482997658328</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.404010284801236</v>
       </c>
       <c r="E53">
-        <v>-20.84380262190696</v>
+        <v>-25.29800965585152</v>
       </c>
       <c r="F53">
-        <v>3.874420816676075</v>
+        <v>0.7819944199758787</v>
       </c>
       <c r="G53">
-        <v>-11.28361124700558</v>
+        <v>-13.76311225550181</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.410263173239482</v>
       </c>
       <c r="E54">
-        <v>-20.48187792226593</v>
+        <v>-24.13366653289535</v>
       </c>
       <c r="F54">
-        <v>3.719868996866161</v>
+        <v>0.5753308352232497</v>
       </c>
       <c r="G54">
-        <v>-11.05651462165485</v>
+        <v>-13.38852143983248</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.421319871692523</v>
       </c>
       <c r="E55">
-        <v>-19.45666763472142</v>
+        <v>-24.37664180577691</v>
       </c>
       <c r="F55">
-        <v>3.59524277784978</v>
+        <v>0.6999197777065037</v>
       </c>
       <c r="G55">
-        <v>-10.98548929977911</v>
+        <v>-14.08545125844776</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.445301051224735</v>
       </c>
       <c r="E56">
-        <v>-19.71502160533302</v>
+        <v>-23.75184824693863</v>
       </c>
       <c r="F56">
-        <v>3.591737127001133</v>
+        <v>0.5851908924187722</v>
       </c>
       <c r="G56">
-        <v>-11.14283699844072</v>
+        <v>-14.16435971512007</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.479028600689402</v>
       </c>
       <c r="E57">
-        <v>-19.2320100392009</v>
+        <v>-23.37137944623619</v>
       </c>
       <c r="F57">
-        <v>3.678907885532531</v>
+        <v>1.117648891590239</v>
       </c>
       <c r="G57">
-        <v>-11.51362159710109</v>
+        <v>-13.75034010058167</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.523971380370197</v>
       </c>
       <c r="E58">
-        <v>-18.29662656207254</v>
+        <v>-24.4391573894528</v>
       </c>
       <c r="F58">
-        <v>3.974480971995034</v>
+        <v>0.5608857644532319</v>
       </c>
       <c r="G58">
-        <v>-11.67348271147724</v>
+        <v>-14.11026385588028</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.570613215012015</v>
       </c>
       <c r="E59">
-        <v>-19.47119950781204</v>
+        <v>-23.53311389542013</v>
       </c>
       <c r="F59">
-        <v>3.753358234226539</v>
+        <v>0.4595051914942116</v>
       </c>
       <c r="G59">
-        <v>-11.66866259700642</v>
+        <v>-13.64304579619861</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.615278686117302</v>
       </c>
       <c r="E60">
-        <v>-18.34427516558124</v>
+        <v>-21.51260841962579</v>
       </c>
       <c r="F60">
-        <v>3.885262489243916</v>
+        <v>0.7731623667272304</v>
       </c>
       <c r="G60">
-        <v>-12.11232968894518</v>
+        <v>-13.43722789266088</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.647672707671545</v>
       </c>
       <c r="E61">
-        <v>-19.30146324505654</v>
+        <v>-22.66624623002783</v>
       </c>
       <c r="F61">
-        <v>3.845991247411996</v>
+        <v>0.5338428822214393</v>
       </c>
       <c r="G61">
-        <v>-12.07234144180022</v>
+        <v>-13.92888284990652</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.659763840894817</v>
       </c>
       <c r="E62">
-        <v>-18.10462379262132</v>
+        <v>-19.37904959022995</v>
       </c>
       <c r="F62">
-        <v>3.678556657753743</v>
+        <v>0.9318858447776437</v>
       </c>
       <c r="G62">
-        <v>-12.43157614057135</v>
+        <v>-14.75861682991876</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.64551843006902</v>
       </c>
       <c r="E63">
-        <v>-16.32019219532084</v>
+        <v>-20.68025225464594</v>
       </c>
       <c r="F63">
-        <v>3.859876341817722</v>
+        <v>0.4469272608501039</v>
       </c>
       <c r="G63">
-        <v>-12.59668392822105</v>
+        <v>-14.0445738002602</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.595662663990337</v>
       </c>
       <c r="E64">
-        <v>-17.48649161904833</v>
+        <v>-21.01312679352776</v>
       </c>
       <c r="F64">
-        <v>3.711808982036922</v>
+        <v>0.6623789953790329</v>
       </c>
       <c r="G64">
-        <v>-12.36095112772586</v>
+        <v>-15.25123974752443</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.5080724469946</v>
       </c>
       <c r="E65">
-        <v>-16.93394533452842</v>
+        <v>-21.2725630694272</v>
       </c>
       <c r="F65">
-        <v>3.714840806731167</v>
+        <v>0.4746941361919433</v>
       </c>
       <c r="G65">
-        <v>-13.11450990862481</v>
+        <v>-15.51003789497174</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.375750051204065</v>
       </c>
       <c r="E66">
-        <v>-17.94655740738359</v>
+        <v>-20.56611659575661</v>
       </c>
       <c r="F66">
-        <v>3.87039495109847</v>
+        <v>0.6903819554306703</v>
       </c>
       <c r="G66">
-        <v>-12.74290172335302</v>
+        <v>-14.06625119049267</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.202191314868006</v>
       </c>
       <c r="E67">
-        <v>-17.58490441618302</v>
+        <v>-21.40277933951776</v>
       </c>
       <c r="F67">
-        <v>3.578658862445734</v>
+        <v>0.8828531214711354</v>
       </c>
       <c r="G67">
-        <v>-12.8315537674461</v>
+        <v>-13.94817643267605</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.984208242898857</v>
       </c>
       <c r="E68">
-        <v>-17.37066231088014</v>
+        <v>-21.68080500121868</v>
       </c>
       <c r="F68">
-        <v>3.365326091733166</v>
+        <v>0.7248586067351857</v>
       </c>
       <c r="G68">
-        <v>-13.16245183682986</v>
+        <v>-15.03863463719099</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.729080642974692</v>
       </c>
       <c r="E69">
-        <v>-18.05039984485348</v>
+        <v>-20.66014583005188</v>
       </c>
       <c r="F69">
-        <v>3.463427986511906</v>
+        <v>0.4578791062825162</v>
       </c>
       <c r="G69">
-        <v>-12.60408636405915</v>
+        <v>-13.62498595273543</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.439352198945821</v>
       </c>
       <c r="E70">
-        <v>-17.05933877980081</v>
+        <v>-20.90833337651626</v>
       </c>
       <c r="F70">
-        <v>3.251355990986399</v>
+        <v>0.08559422811636236</v>
       </c>
       <c r="G70">
-        <v>-12.53407165842372</v>
+        <v>-15.91413017368203</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.120414036869342</v>
       </c>
       <c r="E71">
-        <v>-17.17332952752189</v>
+        <v>-21.70518630527598</v>
       </c>
       <c r="F71">
-        <v>2.942398144029462</v>
+        <v>-0.1127898244452856</v>
       </c>
       <c r="G71">
-        <v>-12.28555521873294</v>
+        <v>-14.89165231743567</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.779888553405199</v>
       </c>
       <c r="E72">
-        <v>-16.32936688366038</v>
+        <v>-21.44919619809638</v>
       </c>
       <c r="F72">
-        <v>3.036068273203225</v>
+        <v>0.4407319010445664</v>
       </c>
       <c r="G72">
-        <v>-12.21761752634464</v>
+        <v>-13.92715692736625</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.422122359437683</v>
       </c>
       <c r="E73">
-        <v>-17.01619147945573</v>
+        <v>-22.46647259917945</v>
       </c>
       <c r="F73">
-        <v>2.666465648687335</v>
+        <v>-0.05293613775600736</v>
       </c>
       <c r="G73">
-        <v>-12.37384632845448</v>
+        <v>-13.22658659343077</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.058692183296825</v>
       </c>
       <c r="E74">
-        <v>-17.50401681345801</v>
+        <v>-21.97890991666961</v>
       </c>
       <c r="F74">
-        <v>3.102892671587061</v>
+        <v>-0.5162146900174784</v>
       </c>
       <c r="G74">
-        <v>-12.31701885226646</v>
+        <v>-13.43172856532725</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.691624245370861</v>
       </c>
       <c r="E75">
-        <v>-17.67107221960097</v>
+        <v>-21.3494293872334</v>
       </c>
       <c r="F75">
-        <v>2.759647041093447</v>
+        <v>-0.3020137902667767</v>
       </c>
       <c r="G75">
-        <v>-11.89933575385694</v>
+        <v>-13.14660025547618</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.334967744241228</v>
       </c>
       <c r="E76">
-        <v>-17.27799614726118</v>
+        <v>-22.64730815172775</v>
       </c>
       <c r="F76">
-        <v>2.627096659501886</v>
+        <v>-0.8586327814756961</v>
       </c>
       <c r="G76">
-        <v>-11.72592647566185</v>
+        <v>-13.07996848926854</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.992006955202151</v>
       </c>
       <c r="E77">
-        <v>-18.89416776433266</v>
+        <v>-22.37364341049621</v>
       </c>
       <c r="F77">
-        <v>2.683727168626872</v>
+        <v>0.4578807630173218</v>
       </c>
       <c r="G77">
-        <v>-11.52213308582629</v>
+        <v>-12.26439133967452</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.671675862897949</v>
       </c>
       <c r="E78">
-        <v>-18.41389139650116</v>
+        <v>-21.96570941493725</v>
       </c>
       <c r="F78">
-        <v>2.673980597765533</v>
+        <v>-0.4188583259012582</v>
       </c>
       <c r="G78">
-        <v>-11.38030556514086</v>
+        <v>-11.77789774394189</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.379628185398398</v>
       </c>
       <c r="E79">
-        <v>-19.01541312741402</v>
+        <v>-22.35419361463327</v>
       </c>
       <c r="F79">
-        <v>2.178881968460324</v>
+        <v>-0.7419564044239829</v>
       </c>
       <c r="G79">
-        <v>-11.12641120331414</v>
+        <v>-12.09841074709001</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.119377003199308</v>
       </c>
       <c r="E80">
-        <v>-19.02235527806778</v>
+        <v>-21.93120697147281</v>
       </c>
       <c r="F80">
-        <v>1.967235753779856</v>
+        <v>-0.2261444482117728</v>
       </c>
       <c r="G80">
-        <v>-10.64098400458833</v>
+        <v>-13.44234331707205</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.896411696163575</v>
       </c>
       <c r="E81">
-        <v>-19.74290794827226</v>
+        <v>-23.30988276921202</v>
       </c>
       <c r="F81">
-        <v>2.229912713942385</v>
+        <v>-0.7553403365510145</v>
       </c>
       <c r="G81">
-        <v>-10.20637308415364</v>
+        <v>-12.25627031631489</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.708061146623546</v>
       </c>
       <c r="E82">
-        <v>-19.73865571117906</v>
+        <v>-23.64366753136939</v>
       </c>
       <c r="F82">
-        <v>2.393818458464712</v>
+        <v>-0.8449879136167826</v>
       </c>
       <c r="G82">
-        <v>-9.667688378296484</v>
+        <v>-11.40237834257124</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.557707347044052</v>
       </c>
       <c r="E83">
-        <v>-21.26787609882926</v>
+        <v>-25.19191656679982</v>
       </c>
       <c r="F83">
-        <v>2.061992700986091</v>
+        <v>-0.8027635419938834</v>
       </c>
       <c r="G83">
-        <v>-9.879684822030647</v>
+        <v>-10.01987501315792</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.438701403197169</v>
       </c>
       <c r="E84">
-        <v>-20.6407911321431</v>
+        <v>-24.72694644111425</v>
       </c>
       <c r="F84">
-        <v>1.775889510672393</v>
+        <v>-1.346824483376362</v>
       </c>
       <c r="G84">
-        <v>-9.545236470919566</v>
+        <v>-10.99701294989588</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.348769997721845</v>
       </c>
       <c r="E85">
-        <v>-22.09842087420604</v>
+        <v>-26.31219763766136</v>
       </c>
       <c r="F85">
-        <v>1.805873097184124</v>
+        <v>-1.051918232673113</v>
       </c>
       <c r="G85">
-        <v>-8.983694775679316</v>
+        <v>-10.63570123787763</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.281494733127148</v>
       </c>
       <c r="E86">
-        <v>-22.990471383555</v>
+        <v>-26.79351555451462</v>
       </c>
       <c r="F86">
-        <v>1.706745683560718</v>
+        <v>-1.982530195632759</v>
       </c>
       <c r="G86">
-        <v>-9.343999152678823</v>
+        <v>-9.74895767388081</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.229671939893312</v>
       </c>
       <c r="E87">
-        <v>-24.0186885778406</v>
+        <v>-27.27097973998735</v>
       </c>
       <c r="F87">
-        <v>1.156878715052017</v>
+        <v>-1.482934359697752</v>
       </c>
       <c r="G87">
-        <v>-8.924435914315746</v>
+        <v>-11.22105147675321</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.188991650468608</v>
       </c>
       <c r="E88">
-        <v>-25.0211613973926</v>
+        <v>-29.9622246719018</v>
       </c>
       <c r="F88">
-        <v>1.332764308953631</v>
+        <v>-1.258377210677251</v>
       </c>
       <c r="G88">
-        <v>-8.067718808809408</v>
+        <v>-10.7505997732247</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.152735564927931</v>
       </c>
       <c r="E89">
-        <v>-27.40611393285025</v>
+        <v>-29.92176954935428</v>
       </c>
       <c r="F89">
-        <v>1.066995881643854</v>
+        <v>-1.748128728397389</v>
       </c>
       <c r="G89">
-        <v>-8.472132647232529</v>
+        <v>-9.696740313983808</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.121329330110964</v>
       </c>
       <c r="E90">
-        <v>-27.22225788813883</v>
+        <v>-30.86993917284329</v>
       </c>
       <c r="F90">
-        <v>0.9303136034471302</v>
+        <v>-1.578779781671266</v>
       </c>
       <c r="G90">
-        <v>-7.794934454464972</v>
+        <v>-9.645149667404658</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.093437018912663</v>
       </c>
       <c r="E91">
-        <v>-29.80040191747471</v>
+        <v>-31.80801482776921</v>
       </c>
       <c r="F91">
-        <v>0.5968924103507181</v>
+        <v>-2.44391510001143</v>
       </c>
       <c r="G91">
-        <v>-7.800128628193573</v>
+        <v>-9.39470715065848</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.074518740115225</v>
       </c>
       <c r="E92">
-        <v>-31.24477455188019</v>
+        <v>-33.27018210078784</v>
       </c>
       <c r="F92">
-        <v>0.5361540272752499</v>
+        <v>-3.057657478950001</v>
       </c>
       <c r="G92">
-        <v>-8.003337960591542</v>
+        <v>-11.00503225538716</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.071149584220453</v>
       </c>
       <c r="E93">
-        <v>-32.52741952981275</v>
+        <v>-36.69006302901045</v>
       </c>
       <c r="F93">
-        <v>-0.2237231302933898</v>
+        <v>-2.955189259591105</v>
       </c>
       <c r="G93">
-        <v>-7.57092873982324</v>
+        <v>-9.681341541205333</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.088282383829665</v>
       </c>
       <c r="E94">
-        <v>-34.87213883794924</v>
+        <v>-37.1285076181961</v>
       </c>
       <c r="F94">
-        <v>-0.451635167295229</v>
+        <v>-2.677494826783224</v>
       </c>
       <c r="G94">
-        <v>-7.594041664487968</v>
+        <v>-10.85087718530289</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.134122236825159</v>
       </c>
       <c r="E95">
-        <v>-36.3944850020558</v>
+        <v>-39.14304003677432</v>
       </c>
       <c r="F95">
-        <v>-0.5759772562924488</v>
+        <v>-3.137941190894523</v>
       </c>
       <c r="G95">
-        <v>-8.07988229713027</v>
+        <v>-10.19605036112763</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.212343347920872</v>
       </c>
       <c r="E96">
-        <v>-38.49036466347082</v>
+        <v>-40.08713629789344</v>
       </c>
       <c r="F96">
-        <v>-0.7461322045014952</v>
+        <v>-3.286185821299523</v>
       </c>
       <c r="G96">
-        <v>-7.630794627175309</v>
+        <v>-10.26634068937405</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.322647450691934</v>
       </c>
       <c r="E97">
-        <v>-40.12828654120114</v>
+        <v>-43.13920098179104</v>
       </c>
       <c r="F97">
-        <v>-1.351608305127529</v>
+        <v>-3.320472776468797</v>
       </c>
       <c r="G97">
-        <v>-7.611737292358054</v>
+        <v>-10.06586789575666</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.464916138680483</v>
       </c>
       <c r="E98">
-        <v>-42.55726490096136</v>
+        <v>-44.61338456058903</v>
       </c>
       <c r="F98">
-        <v>-1.787543277789992</v>
+        <v>-3.741043190544134</v>
       </c>
       <c r="G98">
-        <v>-8.029807574911583</v>
+        <v>-10.90038097497023</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.624731158897588</v>
       </c>
       <c r="E99">
-        <v>-45.09764598554727</v>
+        <v>-45.26921628027588</v>
       </c>
       <c r="F99">
-        <v>-1.850065135883687</v>
+        <v>-4.325207054630943</v>
       </c>
       <c r="G99">
-        <v>-8.117038850069422</v>
+        <v>-11.18252665442377</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.803254188076663</v>
       </c>
       <c r="E100">
-        <v>-46.57703278098007</v>
+        <v>-48.60702314558348</v>
       </c>
       <c r="F100">
-        <v>-2.132051340205472</v>
+        <v>-4.606556244419975</v>
       </c>
       <c r="G100">
-        <v>-8.225804782321894</v>
+        <v>-11.58419082918007</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.965842752714472</v>
       </c>
       <c r="E101">
-        <v>-48.94216871418015</v>
+        <v>-50.01585178750276</v>
       </c>
       <c r="F101">
-        <v>-2.476615731604344</v>
+        <v>-4.296952270888855</v>
       </c>
       <c r="G101">
-        <v>-8.488381256394899</v>
+        <v>-11.29572551700305</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.135013741748746</v>
       </c>
       <c r="E102">
-        <v>-51.36648387783097</v>
+        <v>-52.46399238502644</v>
       </c>
       <c r="F102">
-        <v>-2.53432643182258</v>
+        <v>-4.643238838118146</v>
       </c>
       <c r="G102">
-        <v>-8.691022937463085</v>
+        <v>-12.5121235674126</v>
       </c>
     </row>
   </sheetData>
